--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104502_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104502_W5.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.861</v>
+        <v>6.2091</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7163</v>
+        <v>3.8193</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1446</v>
+        <v>2.3899</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3372</v>
+        <v>3.3419</v>
       </c>
       <c r="H2" t="n">
-        <v>1.642</v>
+        <v>1.6482</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6953</v>
+        <v>1.6936</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1685</v>
+        <v>3.1531</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1688</v>
+        <v>0.1887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3215</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3871</v>
+        <v>0.5084</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.1524</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5511</v>
+        <v>4.1498</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1935</v>
+        <v>3.9706</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3575</v>
+        <v>0.1792</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8261</v>
+        <v>-0.0556</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6448</v>
+        <v>1.7265</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1813</v>
+        <v>-1.7821</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8146</v>
+        <v>1.8781</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1429</v>
+        <v>2.8473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6717</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0115</v>
+        <v>-1.9337</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5019</v>
+        <v>-1.1209</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4904</v>
+        <v>-0.8129</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6569</v>
+        <v>0.2753</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1916</v>
+        <v>0.894</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5347</v>
+        <v>-0.6187</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>2.3367</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4017</v>
+        <v>3.2182</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7527</v>
+        <v>1.8977</v>
       </c>
       <c r="F4" t="n">
-        <v>1.649</v>
+        <v>1.3205</v>
       </c>
       <c r="G4" t="n">
+        <v>1.8387</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.6538</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.6782</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.9756</v>
+        <v>0.1849</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3656</v>
+        <v>1.8079</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0968</v>
+        <v>1.1376</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2688</v>
+        <v>0.6703</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2883</v>
+        <v>0.0308</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5814</v>
+        <v>0.5162</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2931</v>
+        <v>-0.4854</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6137</v>
+        <v>0.3112</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3871</v>
+        <v>0.9125</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2265</v>
+        <v>-0.6012</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2311</v>
+        <v>3.2095</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3312</v>
+        <v>1.5085</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8999</v>
+        <v>1.701</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0828</v>
+        <v>1.6613</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0492</v>
+        <v>0.6778</v>
       </c>
       <c r="I5" t="n">
-        <v>3.132</v>
+        <v>0.9835</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6117</v>
+        <v>1.3555</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1487</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4629</v>
+        <v>1.2661</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5289</v>
+        <v>0.3058</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.198</v>
+        <v>0.5884</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6691</v>
+        <v>-0.2826</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5093</v>
+        <v>0.4101</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8953</v>
+        <v>0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3859</v>
+        <v>0.257</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0716</v>
+        <v>3.026</v>
       </c>
       <c r="E6" t="n">
-        <v>2.891</v>
+        <v>1.432</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1806</v>
+        <v>1.594</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0369</v>
+        <v>1.0363</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7331</v>
+        <v>2.6195</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.77</v>
+        <v>-1.5832</v>
       </c>
       <c r="J6" t="n">
-        <v>1.921</v>
+        <v>1.9066</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8675</v>
+        <v>2.7784</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.9464</v>
+        <v>-0.8718</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9579</v>
+        <v>-0.8703</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1344</v>
+        <v>-0.1588</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8236</v>
+        <v>-0.7114</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8254</v>
+        <v>-0.0104</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2419</v>
+        <v>0.348</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5834</v>
+        <v>-0.3584</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3461</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8203</v>
+        <v>2.8309</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2307</v>
+        <v>2.0271</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5896</v>
+        <v>0.8038</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0347</v>
+        <v>2.0968</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6234</v>
+        <v>-1.0375</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5886</v>
+        <v>3.1343</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9345</v>
+        <v>2.5988</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7982</v>
+        <v>0.1411</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8637</v>
+        <v>2.4576</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8998</v>
+        <v>-0.502</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1749</v>
+        <v>-1.1786</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7249</v>
+        <v>0.6766</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2144</v>
+        <v>0.0999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1089</v>
+        <v>0.6151</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3233</v>
+        <v>-0.5152</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5019</v>
+        <v>2.6123</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06610000000000001</v>
+        <v>1.0554</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4358</v>
+        <v>1.5569</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9576</v>
+        <v>2.9619</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6492</v>
+        <v>0.6545</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3083</v>
+        <v>2.3074</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0633</v>
+        <v>3.0441</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3046</v>
+        <v>0.2963</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7587</v>
+        <v>2.7479</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1057</v>
+        <v>-0.0822</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.002</v>
+        <v>0.1057</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7289</v>
+        <v>0.2876</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2731</v>
+        <v>-0.1819</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.287</v>
+        <v>-0.1089</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6096</v>
+        <v>1.079</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8966</v>
+        <v>-1.1878</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6116</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7618</v>
+        <v>-0.9709</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8498</v>
+        <v>1.546</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.9913</v>
+        <v>1.5785</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2796</v>
+        <v>0.1789</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7117</v>
+        <v>1.3997</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6203</v>
+        <v>-1.0034</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5178</v>
+        <v>-1.1497</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1381</v>
+        <v>0.1463</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7548</v>
+        <v>-0.0011</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9599</v>
+        <v>0.6873</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2051</v>
+        <v>-0.6884</v>
       </c>
       <c r="V9" t="n">
-        <v>3.278</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.8243</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2754</v>
+        <v>-1.043</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5859</v>
+        <v>-1.5915</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3105</v>
+        <v>0.5486</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5787</v>
+        <v>-3.61</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9726</v>
+        <v>-1.7661</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5513</v>
+        <v>-1.8439</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6062</v>
+        <v>-3.0119</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1936</v>
+        <v>-2.2967</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4126</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0275</v>
+        <v>-0.5981</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1662</v>
+        <v>0.5306</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1387</v>
+        <v>-1.1287</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3771</v>
+        <v>0.4367</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1553</v>
+        <v>1.0217</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7782</v>
+        <v>-0.5849</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>3.8132</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2557</v>
+        <v>-1.1327</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5537</v>
+        <v>-3.7665</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8094</v>
+        <v>2.6338</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5457</v>
+        <v>-1.4638</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6421</v>
+        <v>-0.2851</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9036</v>
+        <v>-1.1787</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.285</v>
+        <v>-1.6384</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4586</v>
+        <v>0.2618</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8264</v>
+        <v>-1.9002</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7392</v>
+        <v>0.1746</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8165</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0772</v>
+        <v>0.7215</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3213</v>
+        <v>0.3311</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8389</v>
+        <v>0.1482</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4824</v>
+        <v>0.1829</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3084</v>
+        <v>-1.3169</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7457</v>
+        <v>-3.9987</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4373</v>
+        <v>2.6819</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4691</v>
+        <v>-1.5432</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2989</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1702</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6094</v>
+        <v>-2.3072</v>
       </c>
       <c r="K12" t="n">
-        <v>0.27</v>
+        <v>-1.4726</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8794</v>
+        <v>-0.8345</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1403</v>
+        <v>0.7639</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5689</v>
+        <v>0.832</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7091</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8393</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.868</v>
+        <v>0.427</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0287</v>
+        <v>0.3245</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5854</v>
+        <v>-2.9402</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0713</v>
+        <v>-4.637</v>
       </c>
       <c r="F13" t="n">
-        <v>1.486</v>
+        <v>1.6968</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4832</v>
+        <v>1.4777</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0995</v>
+        <v>1.1027</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3838</v>
+        <v>0.375</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0914</v>
+        <v>0.0692</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3919</v>
+        <v>1.4085</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0373</v>
+        <v>1.0477</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8003</v>
+        <v>-0.1416</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6261</v>
+        <v>-0.1535</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1742</v>
+        <v>0.0119</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.363</v>
+        <v>18.7141</v>
       </c>
       <c r="E14" t="n">
-        <v>2.787099999999999</v>
+        <v>2.7959</v>
       </c>
       <c r="F14" t="n">
-        <v>15.5758</v>
+        <v>15.9186</v>
       </c>
       <c r="G14" t="n">
-        <v>8.290800000000001</v>
+        <v>8.3171</v>
       </c>
       <c r="H14" t="n">
-        <v>5.345600000000001</v>
+        <v>5.3828</v>
       </c>
       <c r="I14" t="n">
-        <v>2.945399999999999</v>
+        <v>2.934099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6911</v>
+        <v>10.4343</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6009</v>
+        <v>5.4644</v>
       </c>
       <c r="L14" t="n">
-        <v>5.0902</v>
+        <v>4.969999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4001</v>
+        <v>-2.1174</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2554999999999998</v>
+        <v>-0.08140000000000014</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1448</v>
+        <v>-2.036</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0001999999999995339</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.6833</v>
+        <v>-22.7632</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6833</v>
+        <v>22.7633</v>
       </c>
       <c r="S14" t="n">
-        <v>2.873199999999999</v>
+        <v>3.2292</v>
       </c>
       <c r="T14" t="n">
-        <v>5.459199999999999</v>
+        <v>5.8494</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.5859</v>
+        <v>-2.620000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>7.198899999999999</v>
+        <v>7.168</v>
       </c>
       <c r="W14" t="n">
-        <v>9.32</v>
+        <v>9.275499999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1212</v>
+        <v>-2.1076</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6182</v>
+        <v>4.349</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8654</v>
+        <v>2.1826</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7528</v>
+        <v>2.1665</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9968</v>
+        <v>3.9959</v>
       </c>
       <c r="H15" t="n">
-        <v>2.472</v>
+        <v>2.4565</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5248</v>
+        <v>1.5394</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6225</v>
+        <v>3.5883</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3164</v>
+        <v>2.285</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3743</v>
+        <v>0.4076</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2187</v>
+        <v>0.2361</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.286</v>
+        <v>-0.5574</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3962</v>
+        <v>-0.04</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8898</v>
+        <v>-0.5174</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4121</v>
+        <v>2.3847</v>
       </c>
       <c r="E16" t="n">
-        <v>1.988</v>
+        <v>0.4547</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4241</v>
+        <v>1.9301</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7748</v>
+        <v>-0.7546</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1181</v>
+        <v>0.1314</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8929</v>
+        <v>-0.886</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1091</v>
+        <v>-1.1173</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3343</v>
+        <v>0.3627</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3061</v>
+        <v>1.2484</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3239</v>
+        <v>1.7996</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0177</v>
+        <v>-0.5512</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3225</v>
+        <v>0.7705</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3471</v>
+        <v>0.2046</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0246</v>
+        <v>0.5658</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0885</v>
+        <v>-0.3102</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3492</v>
+        <v>-0.4887</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2608</v>
+        <v>0.1785</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3028</v>
+        <v>0.9645</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6814</v>
+        <v>0.0862</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3786</v>
+        <v>0.8783</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2143</v>
+        <v>-1.2747</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3321</v>
+        <v>-0.5749</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8822</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0318</v>
+        <v>-0.4136</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3107</v>
+        <v>-0.5323</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2789</v>
+        <v>0.1187</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.571</v>
+        <v>-0.3268</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7997</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3129</v>
+        <v>0.3283</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1362</v>
+        <v>1.248</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4491</v>
+        <v>-0.9197</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3126</v>
+        <v>2.0836</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4965</v>
+        <v>3.3407</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1839</v>
+        <v>-1.2571</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9768</v>
+        <v>3.2698</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0866</v>
+        <v>3.6575</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8902</v>
+        <v>-0.3877</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2894</v>
+        <v>-1.1861</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5831</v>
+        <v>-0.3168</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>-0.8694</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8614000000000001</v>
+        <v>1.0382</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8861</v>
+        <v>1.2561</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0248</v>
+        <v>-0.2179</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3278</v>
+        <v>-2.5659</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3278</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8567</v>
+        <v>-0.4929</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0607</v>
+        <v>-0.8298</v>
       </c>
       <c r="F19" t="n">
-        <v>0.204</v>
+        <v>0.3369</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8821</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0721</v>
+        <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8024</v>
+        <v>0.8076</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3517</v>
+        <v>0.3503</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5228</v>
+        <v>0.5319</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8239</v>
+        <v>-0.4645</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2782</v>
+        <v>-0.0419</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5456</v>
+        <v>-0.4226</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3319</v>
+        <v>-1.1463</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5795</v>
+        <v>-1.3897</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2476</v>
+        <v>0.2434</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4351</v>
+        <v>-0.4479</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0074</v>
+        <v>-0.0023</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4425</v>
+        <v>-0.4455</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9543</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1345</v>
+        <v>0.1132</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4225</v>
+        <v>-1.4022</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5275</v>
+        <v>-0.3229</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0302</v>
+        <v>0.2086</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4972</v>
+        <v>-0.5315</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7649</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3278</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1526</v>
+        <v>-2.0575</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7459</v>
+        <v>-1.7526</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4067</v>
+        <v>-0.3048</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1604</v>
+        <v>-2.1633</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5713</v>
+        <v>-1.5765</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.605</v>
+        <v>-0.6012</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2852</v>
+        <v>-0.1917</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1905</v>
+        <v>-0.1906</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4105</v>
+        <v>-2.0827</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3074</v>
+        <v>-0.2296</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1031</v>
+        <v>-1.8531</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1887</v>
+        <v>-2.2035</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4529</v>
+        <v>-1.4614</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7357</v>
+        <v>-0.7421</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.148</v>
+        <v>-0.1829</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1772</v>
+        <v>-0.1971</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0407</v>
+        <v>-2.0207</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5148</v>
+        <v>-0.1767</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1179</v>
+        <v>0.0019</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3968</v>
+        <v>-0.1786</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. DE SOUSA</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9753</v>
+        <v>-2.4696</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3178</v>
+        <v>-1.888</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6575</v>
+        <v>-0.5816</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6232</v>
+        <v>1.8777</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.378</v>
+        <v>-1.0165</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2452</v>
+        <v>2.8942</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2779</v>
+        <v>2.6509</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4644</v>
+        <v>-0.0969</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1866</v>
+        <v>2.7479</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3453</v>
+        <v>-0.7733</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9135</v>
+        <v>-0.9196</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4318</v>
+        <v>0.1463</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-5.0079</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3853</v>
+        <v>0.7096</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1603</v>
+        <v>0.4689</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5456</v>
+        <v>0.2407</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4205</v>
+        <v>-1.1871</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5812</v>
+        <v>-1.1871</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>S. DE SOUSA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9794</v>
+        <v>-2.569</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0852</v>
+        <v>-1.2172</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8942</v>
+        <v>-1.3517</v>
       </c>
       <c r="G24" t="n">
-        <v>1.8845</v>
+        <v>-1.624</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0129</v>
+        <v>-1.3813</v>
       </c>
       <c r="I24" t="n">
-        <v>2.8974</v>
+        <v>-0.2427</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6753</v>
+        <v>-0.2899</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0835</v>
+        <v>-0.4761</v>
       </c>
       <c r="L24" t="n">
-        <v>2.7587</v>
+        <v>0.1862</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-1.334</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9294</v>
+        <v>-0.9052</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1387</v>
+        <v>-0.4289</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.8562</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.9903</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1878</v>
+        <v>0.0161</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2299</v>
+        <v>0.2808</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0421</v>
+        <v>-0.2647</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1956</v>
+        <v>-1.4163</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1956</v>
+        <v>-1.5741</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.865</v>
+        <v>-6.3115</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6745</v>
+        <v>-6.1616</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1906</v>
+        <v>-0.1499</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.5701</v>
+        <v>-4.0763</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.5408</v>
+        <v>0.089</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0293</v>
+        <v>-4.1653</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.7267</v>
+        <v>-2.7498</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.5796</v>
+        <v>0.32</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8529</v>
+        <v>-3.0699</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8434</v>
+        <v>-1.3265</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.231</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8822</v>
+        <v>-1.0954</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-3.8697</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>4.325</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1588</v>
+        <v>-0.7294</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3206</v>
+        <v>-0.0868</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1618</v>
+        <v>-0.6427</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.9611</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.4572</v>
+        <v>-6.6999</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.8691</v>
+        <v>-6.5397</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.1602</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.0703</v>
+        <v>-5.5767</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08799999999999999</v>
+        <v>-5.5484</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.1583</v>
+        <v>-0.0283</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.6993</v>
+        <v>-3.7588</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3423</v>
+        <v>-4.6</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.0416</v>
+        <v>0.8411</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.371</v>
+        <v>-1.8179</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2543</v>
+        <v>-0.9485</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.1167</v>
+        <v>-0.8694</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.8562</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>4.3098</v>
+        <v>1.8211</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.8738</v>
+        <v>-0.6679</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.86</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0138</v>
+        <v>-0.1634</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.9668</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.5131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.3629</v>
+        <v>-15.9969</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.5758</v>
+        <v>-15.9183</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.7873</v>
+        <v>-0.07829999999999912</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.290900000000001</v>
+        <v>-8.3172</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.3456</v>
+        <v>-5.383</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.9453</v>
+        <v>-2.9341</v>
       </c>
       <c r="J27" t="n">
-        <v>2.4001</v>
+        <v>2.117400000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2552999999999994</v>
+        <v>0.08140000000000125</v>
       </c>
       <c r="L27" t="n">
-        <v>2.144900000000001</v>
+        <v>2.0359</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.691</v>
+        <v>-10.4344</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.6009</v>
+        <v>-5.4643</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.0903</v>
+        <v>-4.97</v>
       </c>
       <c r="P27" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>0.0001999999999997004</v>
       </c>
       <c r="Q27" t="n">
-        <v>-22.6833</v>
+        <v>-22.7631</v>
       </c>
       <c r="R27" t="n">
-        <v>22.6833</v>
+        <v>22.7632</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.8734</v>
+        <v>-0.5118000000000004</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5863</v>
+        <v>2.619800000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.4592</v>
+        <v>-3.131699999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.1989</v>
+        <v>-7.168</v>
       </c>
       <c r="W27" t="n">
-        <v>2.1212</v>
+        <v>2.1076</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.32</v>
+        <v>-9.275400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104502_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104502_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-2.1076</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.1871</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.5741</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.5058</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104502_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-9.275400000000001</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
